--- a/input/Domains/Game/AchieveTable.xlsx
+++ b/input/Domains/Game/AchieveTable.xlsx
@@ -8,95 +8,86 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D31520-2202-B14E-BF0B-D0199C6FB766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42009FAE-DAAA-0341-8B07-1CD9A126A5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="500" windowWidth="36980" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35240" yWindow="0" windowWidth="36980" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ACHIEVE_ONCE" sheetId="4" r:id="rId1"/>
-    <sheet name="ACHIEVE_PASS" sheetId="5" r:id="rId2"/>
-    <sheet name="REWARD@ACHIEVE" sheetId="10" r:id="rId3"/>
+    <sheet name="ACHIEVE_SOCIAL" sheetId="1" r:id="rId1"/>
+    <sheet name="ACHIEVE_PASS" sheetId="2" r:id="rId2"/>
+    <sheet name="REWARD@ACHIEVE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="64">
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>achieveId</t>
+  </si>
   <si>
     <t>isActive</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>orderNum</t>
+  </si>
+  <si>
+    <t>reqMsgId</t>
+  </si>
+  <si>
+    <t>reqValue</t>
+  </si>
+  <si>
+    <t>conditionMsgId</t>
+  </si>
+  <si>
+    <t>conditionOp</t>
+  </si>
+  <si>
+    <t>conditionValue</t>
+  </si>
+  <si>
     <t>rewardGroupId</t>
   </si>
   <si>
+    <t>appleAchievementId</t>
+  </si>
+  <si>
+    <t>googleAchievementId</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
-    <t>int</t>
+    <t>class:CBigInt</t>
+  </si>
+  <si>
+    <t>GAME_MESSAGE_OP_TYPE</t>
   </si>
   <si>
     <t>pk</t>
   </si>
   <si>
+    <t>group:true</t>
+  </si>
+  <si>
+    <t>내부 업적 ID (정본)</t>
+  </si>
+  <si>
     <t>운영 활성 토글</t>
-  </si>
-  <si>
-    <t>RewardGroupId (정본)</t>
-  </si>
-  <si>
-    <t>orderNum</t>
-  </si>
-  <si>
-    <t>conditionMsgId</t>
-  </si>
-  <si>
-    <t>conditionOp</t>
-  </si>
-  <si>
-    <t>conditionValue</t>
-  </si>
-  <si>
-    <t>GAME_MESSAGE_OP_TYPE</t>
-  </si>
-  <si>
-    <t>class:CBigInt</t>
-  </si>
-  <si>
-    <t>NONE/EQ/GTE/LTE</t>
-  </si>
-  <si>
-    <t>GTE</t>
-  </si>
-  <si>
-    <t>group:true</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>achieveId</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>reqMsgId</t>
-  </si>
-  <si>
-    <t>reqValue</t>
-  </si>
-  <si>
-    <t>appleAchievementId</t>
-  </si>
-  <si>
-    <t>googleAchievementId</t>
-  </si>
-  <si>
-    <t>내부 업적 ID (정본)</t>
   </si>
   <si>
     <t>업적 단계</t>
@@ -106,10 +97,16 @@
 같은 achieveId group은 같은 값을 사용한다.</t>
   </si>
   <si>
+    <t>NONE/EQ/GTE/LTE</t>
+  </si>
+  <si>
     <t>조건 목표값_x000D__x000D__x000D__x000D__x000D_
 {base, pow}</t>
   </si>
   <si>
+    <t>RewardGroupId (정본)</t>
+  </si>
+  <si>
     <t>Apple Game Center Achievement ID (achieveId group 공통)</t>
   </si>
   <si>
@@ -119,7 +116,7 @@
     <t>achieve_001</t>
   </si>
   <si>
-    <t>msg_achieve_001_sum</t>
+    <t>GTE</t>
   </si>
   <si>
     <t>reward_mission_achieve_001</t>
@@ -128,45 +125,21 @@
     <t>CgkIi_C0k7wDEAIQBg</t>
   </si>
   <si>
-    <t>reward_mission_achieve_002</t>
-  </si>
-  <si>
-    <t>reward_mission_achieve_003</t>
-  </si>
-  <si>
-    <t>reward_mission_achieve_004</t>
-  </si>
-  <si>
-    <t>reward_mission_achieve_005</t>
-  </si>
-  <si>
     <t>achieve_002</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>msg_achieve_002_sum</t>
-  </si>
-  <si>
     <t>achieve_003</t>
   </si>
   <si>
-    <t>msg_achieve_003_sum</t>
-  </si>
-  <si>
     <t>achieve_004</t>
   </si>
   <si>
-    <t>msg_achieve_004_sum</t>
-  </si>
-  <si>
     <t>achieve_005</t>
   </si>
   <si>
-    <t>msg_achieve_005_sum</t>
-  </si>
-  <si>
     <t>reqSeasonId</t>
   </si>
   <si>
@@ -227,17 +200,23 @@
     <t>Amount</t>
   </si>
   <si>
+    <t>reward_achieve_001</t>
+  </si>
+  <si>
     <t>CURRENCY</t>
   </si>
   <si>
     <t>JEWEL_FREE</t>
   </si>
   <si>
-    <t>reward_achieve_001</t>
+    <t>reward_achieve_002</t>
+  </si>
+  <si>
+    <t>msg_achieve_001_total</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>reward_achieve_002</t>
+    <t>msg_achieve_001_total</t>
   </si>
 </sst>
 </file>
@@ -620,7 +599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
@@ -632,121 +611,121 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
       <c r="M1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>28</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -754,31 +733,31 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
       <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
         <v>32</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -786,7 +765,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -798,16 +777,16 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J6">
         <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -815,7 +794,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -827,16 +806,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J7">
         <v>200</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -844,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -856,16 +835,16 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>1000</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -873,7 +852,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -885,16 +864,16 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J9">
         <v>5000</v>
       </c>
       <c r="K9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -902,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -914,22 +893,22 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -937,7 +916,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -949,22 +928,22 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -972,7 +951,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -984,22 +963,22 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1007,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -1019,22 +998,22 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1044,118 +1023,119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1163,7 +1143,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -1175,10 +1155,19 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1186,7 +1175,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -1198,10 +1187,19 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1209,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -1221,10 +1219,19 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1232,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -1244,10 +1251,19 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1255,7 +1271,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -1267,10 +1283,19 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1278,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -1290,13 +1315,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1304,7 +1329,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -1316,13 +1341,13 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K11" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1330,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -1342,13 +1367,13 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1356,7 +1381,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -1368,13 +1393,13 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1382,7 +1407,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -1394,13 +1419,13 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1410,7 +1435,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
@@ -1419,67 +1444,67 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1487,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E5">
         <v>1000</v>
@@ -1507,13 +1532,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>100</v>
